--- a/EndResult/50m Bryst.xlsx
+++ b/EndResult/50m Bryst.xlsx
@@ -1343,25 +1343,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rebekka Wangberg</t>
+          <t>Maria Erikovna Alvestad</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>33,46</t>
+          <t>33,18</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17.11.2017</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maria Erikovna Alvestad</t>
+          <t>Rebekka Wangberg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.09.2023</t>
+          <t>17.11.2017</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/EndResult/50m Bryst.xlsx
+++ b/EndResult/50m Bryst.xlsx
@@ -1012,25 +1012,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ådne Viken Refseth</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,34</t>
+          <t>30,65</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14.07.2016</t>
+          <t>19.04.2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1047,25 +1047,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tudor Ignat</t>
+          <t>Ådne Viken Refseth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31,37</t>
+          <t>31,34</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.08.2023</t>
+          <t>14.07.2016</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kyushu</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1082,25 +1082,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Tudor Ignat</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31,38</t>
+          <t>31,37</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>04.07.2024</t>
+          <t>11.08.2023</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Kyushu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1152,25 +1152,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32,66</t>
+          <t>32,64</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29.04.2018</t>
+          <t>04.07.2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1187,25 +1187,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Scott Rene Høgenhaug</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32,76</t>
+          <t>32,66</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.05.2015</t>
+          <t>29.04.2018</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1884,25 +1884,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sara Juul Wolfgang</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34,89</t>
+          <t>34,46</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>06.07.2015</t>
+          <t>04.07.2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1919,20 +1919,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Sara Juul Wolfgang</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>35,61</t>
+          <t>34,89</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>549</v>
+        <v>583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.04.2018</t>
+          <t>06.07.2015</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1954,25 +1954,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>35,77</t>
+          <t>35,03</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>541</v>
+        <v>576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.07.2014</t>
+          <t>04.07.2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Drammen</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1989,25 +1989,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alma van der Hagen</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>36,08</t>
+          <t>35,52</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05.04.2025</t>
+          <t>04.07.2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
